--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -10,12 +10,14 @@
     <sheet name="ITT_Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Seguridad" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Movilidad" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cohesion_Social_DesSocial" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Entorno_Urbano_NDVI_arbol" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Educacion_fuera_alcance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Desarrollo_Economico" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Indicadores_Trimestrales" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Auditoria_Spatial_Join" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cohesion_y_Educacion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Educacion_LiceoDptal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Entorno_Urbano" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vivienda_SecVivienda" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Vivienda_Resumen" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Desarrollo_Economico" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Indicadores_Trimestrales" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Auditoria_Spatial_Join" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +445,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -490,7 +492,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>nota_estado</t>
+          <t>cobertura</t>
         </is>
       </c>
     </row>
@@ -505,25 +507,25 @@
         <v>36.04</v>
       </c>
       <c r="D2" t="n">
-        <v>55.18</v>
+        <v>68.37</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>26.35</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>54.91</v>
       </c>
       <c r="G2" t="n">
-        <v>27.99</v>
+        <v>43.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Activacion</t>
+          <t>Consolidacion</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Año completo</t>
         </is>
       </c>
     </row>
@@ -538,25 +540,25 @@
         <v>50.33</v>
       </c>
       <c r="D3" t="n">
-        <v>72.02</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>26.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>58.13</v>
       </c>
       <c r="G3" t="n">
-        <v>37.9</v>
+        <v>50.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Activacion</t>
+          <t>Consolidacion</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Año completo</t>
         </is>
       </c>
     </row>
@@ -571,25 +573,25 @@
         <v>53.63</v>
       </c>
       <c r="D4" t="n">
-        <v>28.45</v>
+        <v>38.9</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>26.35</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>64.36</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>48.12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Activacion</t>
+          <t>Consolidacion</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Año completo</t>
         </is>
       </c>
     </row>
@@ -598,31 +600,811 @@
         <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>96.67</v>
+        <v>90</v>
       </c>
       <c r="C5" t="n">
         <v>95.83</v>
       </c>
       <c r="D5" t="n">
-        <v>90.06</v>
+        <v>64.63</v>
       </c>
       <c r="E5" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Transformacion</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026: datos a la fecha (seguridad/cohesión hasta Q3, movilidad hasta Q2) — guía</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>año</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>trimestre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>homicidios</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hurtos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>siniestralidad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lesionados</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mortales</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>vif</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rinas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>spa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>164</v>
+      </c>
+      <c r="J2" t="n">
+        <v>219</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>410</v>
+      </c>
+      <c r="E3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>185</v>
+      </c>
+      <c r="J3" t="n">
+        <v>155</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>410</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F4" t="n">
+        <v>47</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" t="n">
+        <v>124</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>410</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
       <c r="F5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>143</v>
+      </c>
+      <c r="J5" t="n">
+        <v>107</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>331</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>355</v>
+      </c>
+      <c r="E7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>149</v>
+      </c>
+      <c r="J7" t="n">
+        <v>70</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>317</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Parcial (no comparable)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Parcial (no comparable) | cobertura incompleta en todas las fuentes | DesEco referencial 2025</t>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>122</v>
+      </c>
+      <c r="J8" t="n">
+        <v>101</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>389</v>
+      </c>
+      <c r="E9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>162</v>
+      </c>
+      <c r="J9" t="n">
+        <v>149</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>266</v>
+      </c>
+      <c r="E10" t="n">
+        <v>37</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>204</v>
+      </c>
+      <c r="J10" t="n">
+        <v>208</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>305</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" t="n">
+        <v>215</v>
+      </c>
+      <c r="J11" t="n">
+        <v>186</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>336</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>302</v>
+      </c>
+      <c r="J12" t="n">
+        <v>205</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>338</v>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>18</v>
+      </c>
+      <c r="I13" t="n">
+        <v>204</v>
+      </c>
+      <c r="J13" t="n">
+        <v>97</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>307</v>
+      </c>
+      <c r="E14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>199</v>
+      </c>
+      <c r="J14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>199</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>203</v>
+      </c>
+      <c r="J15" t="n">
+        <v>76</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>241</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
+        <v>182</v>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>metodo_espacial</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Homicidios</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sjoin within al polígono</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hurtos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>sjoin within al polígono</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Comparendos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sjoin within al polígono</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sjoin within al polígono</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Siniestros</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sjoin within al polígono</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Desarrollo Económico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sjoin within (Cámara geocodificada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vivienda (SISBÉN)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sjoin + prorrateo por área (shapefile SISBÉN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Educación (Liceo Dptal)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sjoin de sedes al polígono (DANE 176001001745)</t>
         </is>
       </c>
     </row>
@@ -745,19 +1527,19 @@
         <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>307</v>
+        <v>747</v>
       </c>
       <c r="D5" t="n">
-        <v>93.33</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>96.67</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -951,7 +1733,9 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,7 +1776,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>score_cohesion_DesSocial</t>
+          <t>score_matricula</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>score_desercion</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>score_DesSocial_total</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1813,13 @@
         <v>41.38</v>
       </c>
       <c r="H2" t="n">
-        <v>55.18</v>
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="J2" t="n">
+        <v>68.37</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +1845,13 @@
         <v>76</v>
       </c>
       <c r="H3" t="n">
-        <v>72.02</v>
+        <v>47.83</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1071,7 +1877,13 @@
         <v>23.69</v>
       </c>
       <c r="H4" t="n">
-        <v>28.45</v>
+        <v>26.09</v>
+      </c>
+      <c r="I4" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.9</v>
       </c>
     </row>
     <row r="5">
@@ -1079,7 +1891,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
         <v>584</v>
@@ -1088,7 +1900,7 @@
         <v>223</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>88.33</v>
       </c>
       <c r="F5" t="n">
         <v>73.70999999999999</v>
@@ -1097,7 +1909,11 @@
         <v>96.45999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>90.06</v>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>64.63</v>
       </c>
     </row>
   </sheetData>
@@ -1111,17 +1927,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1132,37 +1949,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ndvi</t>
+          <t>matricula</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>arbolado</t>
+          <t>desertores</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>score_ndvi</t>
+          <t>repitentes</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>score_arbolado</t>
+          <t>tasa_desercion</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>score_entorno_u</t>
+          <t>tasa_repitencia</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>score_matricula</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>score_desercion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>score_educ_des</t>
         </is>
       </c>
     </row>
@@ -1170,104 +1992,110 @@
       <c r="A2" t="n">
         <v>2023</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>2172</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="D2" t="n">
+        <v>140</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NDVI medio anual (satelital) + censo arboreo vivo (corte unico). score_entorno_u = mean(score_ndvi, score_arbolado).</t>
-        </is>
+        <v>6.45</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2024</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>2112</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>106</v>
+      </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NDVI medio anual (satelital) + censo arboreo vivo (corte unico). score_entorno_u = mean(score_ndvi, score_arbolado).</t>
-        </is>
+        <v>5.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="H3" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2025</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2087</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>98</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NDVI medio anual (satelital) + censo arboreo vivo (corte unico). score_entorno_u = mean(score_ndvi, score_arbolado).</t>
-        </is>
+        <v>4.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="H4" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>79.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2026</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
+      <c r="B5" t="n">
+        <v>2057</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>138</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NDVI medio anual (satelital) + censo arboreo vivo (corte unico). score_entorno_u = mean(score_ndvi, score_arbolado).</t>
-        </is>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>66.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1281,37 +2109,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>año</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ndvi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>arbolado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>score_ndvi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>score_arbolado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>score_habitabilidad</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score_entorno_u</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Educacion y Desarrollo NO se calcula en este repositorio.</t>
+      <c r="A2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NDVI medio anual (satelital) + censo arbóreo + habitabilidad (1 - déficit habitacional 2024). score_entorno_u = mean(score_ndvi, score_arbolado, score_habitabilidad). Vivienda es corte único estructural 2024 (constante en la serie).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Se gestiona en otro repositorio (indicacion del usuario, 2026-10-04).</t>
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NDVI medio anual (satelital) + censo arbóreo + habitabilidad (1 - déficit habitacional 2024). score_entorno_u = mean(score_ndvi, score_arbolado, score_habitabilidad). Vivienda es corte único estructural 2024 (constante en la serie).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>La dimension DesSocial de este notebook usa unicamente VIF + Rinas + SPA.</t>
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NDVI medio anual (satelital) + censo arbóreo + habitabilidad (1 - déficit habitacional 2024). score_entorno_u = mean(score_ndvi, score_arbolado, score_habitabilidad). Vivienda es corte único estructural 2024 (constante en la serie).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NDVI anual + censo arbóreo (datos propios de la zona)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NDVI medio anual (satelital) + censo arbóreo + habitabilidad (1 - déficit habitacional 2024). score_entorno_u = mean(score_ndvi, score_arbolado, score_habitabilidad). Vivienda es corte único estructural 2024 (constante en la serie).</t>
         </is>
       </c>
     </row>
@@ -1326,191 +2297,507 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>año</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tipo_dato</t>
+          <t>total_hogares</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>establecimientos_activos</t>
+          <t>deficit_habitacional</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>empleabilidad_total</t>
+          <t>deficit_cuant</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ingresos_operacionales</t>
+          <t>deficit_cualit</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ingresos_log1p</t>
+          <t>pct_area_en_poligono</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>score_establecimientos</t>
+          <t>hogares_prorrateados</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>score_empleabilidad</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>score_ingresos</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>score_des_eco</t>
+          <t>deficit_prorrateado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Proxy retrospectivo (stock acumulado hasta ese año)</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>San Fernando Viejo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>144</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.221</v>
+      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>31.804</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
+        <v>18.111</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Proxy retrospectivo (stock acumulado hasta ese año)</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>El Cedro</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>123</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.419</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>51.525</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
+        <v>21.783</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3 de Julio</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.593</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>26.664</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
+        <v>8.888</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Proxy referencial = 2025 (sin corte 2026 disponible)</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Champagnat</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58.508</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27.944</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Santa Isabel</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17.981</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.679</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Urbanización Colseguros</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>153</v>
+      </c>
+      <c r="C7" t="n">
+        <v>59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Fernando Nuevo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>77</v>
+      </c>
+      <c r="C8" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Eucarístico</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>62</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Urbanización Nueva Granada</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>77</v>
+      </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34.444</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14.762</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Olímpico</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>111</v>
+      </c>
+      <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Urbanización Tequendama</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13.881</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.981999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>El Lido</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>180</v>
+      </c>
+      <c r="C13" t="n">
+        <v>115</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>91</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Los Cámbulos</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>68</v>
+      </c>
+      <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="G14" t="n">
+        <v>67.446</v>
+      </c>
+      <c r="H14" t="n">
+        <v>35.707</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Departamental</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>189</v>
+      </c>
+      <c r="C15" t="n">
+        <v>94</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.715</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nueva Tequendama</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.113</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.019</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Urbanización Militar</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.636</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.254</v>
       </c>
     </row>
   </sheetData>
@@ -1524,646 +2811,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>año</t>
+          <t>indicador</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>trimestre</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>homicidios</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hurtos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>siniestralidad</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lesionados</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>mortales</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vif</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>rinas</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>spa</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>periodo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2023</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Barrios que intersectan el polígono</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>399</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" t="n">
-        <v>164</v>
-      </c>
-      <c r="J2" t="n">
-        <v>219</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2023-Q1</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2023</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hogares (prorrateados)</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>410</v>
-      </c>
-      <c r="E3" t="n">
-        <v>52</v>
-      </c>
-      <c r="F3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" t="n">
-        <v>185</v>
-      </c>
-      <c r="J3" t="n">
-        <v>155</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2023-Q2</t>
-        </is>
+        <v>455</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2023</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Déficit (prorrateado)</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>410</v>
-      </c>
-      <c r="E4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F4" t="n">
-        <v>47</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I4" t="n">
-        <v>124</v>
-      </c>
-      <c r="J4" t="n">
-        <v>100</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2023-Q3</t>
-        </is>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>410</v>
-      </c>
-      <c r="E5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>143</v>
-      </c>
-      <c r="J5" t="n">
-        <v>107</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2023-Q4</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tasa de déficit habitacional</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2024</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Habitabilidad (score, 1-tasa)</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>331</v>
-      </c>
-      <c r="E6" t="n">
-        <v>39</v>
-      </c>
-      <c r="F6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>130</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2024-Q1</t>
-        </is>
+        <v>52.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>355</v>
-      </c>
-      <c r="E7" t="n">
-        <v>47</v>
-      </c>
-      <c r="F7" t="n">
-        <v>43</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>149</v>
-      </c>
-      <c r="J7" t="n">
-        <v>70</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2024-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>317</v>
-      </c>
-      <c r="E8" t="n">
-        <v>37</v>
-      </c>
-      <c r="F8" t="n">
-        <v>35</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>16</v>
-      </c>
-      <c r="I8" t="n">
-        <v>122</v>
-      </c>
-      <c r="J8" t="n">
-        <v>101</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2024-Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>389</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F9" t="n">
-        <v>38</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I9" t="n">
-        <v>162</v>
-      </c>
-      <c r="J9" t="n">
-        <v>149</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2024-Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>266</v>
-      </c>
-      <c r="E10" t="n">
-        <v>37</v>
-      </c>
-      <c r="F10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>204</v>
-      </c>
-      <c r="J10" t="n">
-        <v>208</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>305</v>
-      </c>
-      <c r="E11" t="n">
-        <v>41</v>
-      </c>
-      <c r="F11" t="n">
-        <v>35</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" t="n">
-        <v>215</v>
-      </c>
-      <c r="J11" t="n">
-        <v>186</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>336</v>
-      </c>
-      <c r="E12" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" t="n">
-        <v>38</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I12" t="n">
-        <v>302</v>
-      </c>
-      <c r="J12" t="n">
-        <v>205</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>338</v>
-      </c>
-      <c r="E13" t="n">
-        <v>24</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" t="n">
-        <v>204</v>
-      </c>
-      <c r="J13" t="n">
-        <v>97</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>307</v>
-      </c>
-      <c r="E14" t="n">
-        <v>31</v>
-      </c>
-      <c r="F14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>199</v>
-      </c>
-      <c r="J14" t="n">
-        <v>70</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>19</v>
-      </c>
-      <c r="F15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>203</v>
-      </c>
-      <c r="J15" t="n">
-        <v>76</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>182</v>
-      </c>
-      <c r="J16" t="n">
-        <v>77</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-Q4</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Subsidios de mejoramiento en la zona</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0 (comuna 19 no aparece en la base de subsidios 2024-jun2026)</t>
         </is>
       </c>
     </row>
@@ -2178,107 +2905,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>año</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>tipo_dato</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>establecimientos_activos</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ingresos_operacionales</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>activo_total</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_personas</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ingresos_log1p</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>activo_log1p</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>score_establecimientos</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>score_ingresos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>score_activo_total</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>score_empleo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>score_des_eco</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Homicidios</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2023</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
+          <t>Real (stock activo, fuente consolidada)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6589730777154</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4029455479065</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="I2" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47.12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>54.91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hurtos</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
+          <t>Real (stock activo, fuente consolidada)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3812</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6761988870853</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4104047355269</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="H3" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>58.13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Comparendos</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2025</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
+          <t>Real (stock activo, fuente consolidada)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3994</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7071287354940</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4771959231158</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>64.36</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VIF</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2026</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Siniestros</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Registro Mercantil</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Censo Arboreo</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Verificado 100% dentro del poligono via geopandas.sjoin (Celda 4B) al momento de esta corrida.</t>
-        </is>
+          <t>Real (stock activo, fuente consolidada)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4126</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7073331276679</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4779203372542</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="J5" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>65.34</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -511,13 +511,13 @@
         <v>68.37</v>
       </c>
       <c r="E2" t="n">
-        <v>26.35</v>
+        <v>48.21</v>
       </c>
       <c r="F2" t="n">
         <v>54.91</v>
       </c>
       <c r="G2" t="n">
-        <v>43.21</v>
+        <v>46.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -544,13 +544,13 @@
         <v>69.93000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>26.35</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>58.13</v>
       </c>
       <c r="G3" t="n">
-        <v>50.7</v>
+        <v>57.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -577,13 +577,13 @@
         <v>38.9</v>
       </c>
       <c r="E4" t="n">
-        <v>26.35</v>
+        <v>62.54</v>
       </c>
       <c r="F4" t="n">
         <v>64.36</v>
       </c>
       <c r="G4" t="n">
-        <v>48.12</v>
+        <v>54.27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -610,13 +610,13 @@
         <v>64.63</v>
       </c>
       <c r="E5" t="n">
-        <v>26.35</v>
+        <v>64.39</v>
       </c>
       <c r="F5" t="n">
         <v>65.34</v>
       </c>
       <c r="G5" t="n">
-        <v>71.94</v>
+        <v>78.41</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -2444,19 +2444,23 @@
       <c r="A2" t="n">
         <v>2023</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0.1787</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>14329</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.2753</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>66.6651</v>
       </c>
       <c r="F2" t="n">
         <v>52.7</v>
       </c>
       <c r="G2" t="n">
-        <v>26.35</v>
+        <v>48.2135</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2473,19 +2477,23 @@
       <c r="A3" t="n">
         <v>2024</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0.2157</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>14329</v>
+      </c>
+      <c r="D3" t="n">
+        <v>72.6712</v>
+      </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>66.6651</v>
       </c>
       <c r="F3" t="n">
         <v>52.7</v>
       </c>
       <c r="G3" t="n">
-        <v>26.35</v>
+        <v>64.0121</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2502,19 +2510,23 @@
       <c r="A4" t="n">
         <v>2025</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0.2122</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>14329</v>
+      </c>
+      <c r="D4" t="n">
+        <v>68.2632</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>66.6651</v>
       </c>
       <c r="F4" t="n">
         <v>52.7</v>
       </c>
       <c r="G4" t="n">
-        <v>26.35</v>
+        <v>62.5428</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2531,19 +2543,23 @@
       <c r="A5" t="n">
         <v>2026</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0.2166</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>14329</v>
+      </c>
+      <c r="D5" t="n">
+        <v>73.7928</v>
+      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>66.6651</v>
       </c>
       <c r="F5" t="n">
         <v>52.7</v>
       </c>
       <c r="G5" t="n">
-        <v>26.35</v>
+        <v>64.386</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -514,10 +514,10 @@
         <v>48.21</v>
       </c>
       <c r="F2" t="n">
-        <v>54.91</v>
+        <v>61.98</v>
       </c>
       <c r="G2" t="n">
-        <v>46.93</v>
+        <v>47.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -547,10 +547,10 @@
         <v>64.01000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>58.13</v>
+        <v>65.19</v>
       </c>
       <c r="G3" t="n">
-        <v>57.1</v>
+        <v>58.16</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -580,10 +580,10 @@
         <v>62.54</v>
       </c>
       <c r="F4" t="n">
-        <v>64.36</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>54.27</v>
+        <v>55.12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -613,10 +613,10 @@
         <v>64.39</v>
       </c>
       <c r="F5" t="n">
-        <v>65.34</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>78.41</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3294,7 +3294,9 @@
       <c r="E2" t="n">
         <v>4029455479065</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>33550</v>
+      </c>
       <c r="G2" t="n">
         <v>29.52</v>
       </c>
@@ -3310,9 +3312,11 @@
       <c r="K2" t="n">
         <v>43.48</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>83.18000000000001</v>
+      </c>
       <c r="M2" t="n">
-        <v>54.91</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="3">
@@ -3333,7 +3337,9 @@
       <c r="E3" t="n">
         <v>4104047355269</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>34846</v>
+      </c>
       <c r="G3" t="n">
         <v>29.54</v>
       </c>
@@ -3349,9 +3355,11 @@
       <c r="K3" t="n">
         <v>44.86</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>86.39</v>
+      </c>
       <c r="M3" t="n">
-        <v>58.13</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="4">
@@ -3372,7 +3380,9 @@
       <c r="E4" t="n">
         <v>4771959231158</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>35074</v>
+      </c>
       <c r="G4" t="n">
         <v>29.59</v>
       </c>
@@ -3388,9 +3398,11 @@
       <c r="K4" t="n">
         <v>56.15</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>86.95999999999999</v>
+      </c>
       <c r="M4" t="n">
-        <v>64.36</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3411,7 +3423,9 @@
       <c r="E5" t="n">
         <v>4779203372542</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>34969</v>
+      </c>
       <c r="G5" t="n">
         <v>29.59</v>
       </c>
@@ -3427,9 +3441,11 @@
       <c r="K5" t="n">
         <v>56.26</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>86.7</v>
+      </c>
       <c r="M5" t="n">
-        <v>65.34</v>
+        <v>70.68000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Vivienda_SecVivienda" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Vivienda_Resumen" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Desarrollo_Economico" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Indicadores_Trimestrales" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Comparacion_Subzonas" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Auditoria_Spatial_Join" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="DE_Sectores_Salud_Dep_Edu" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Indicadores_Trimestrales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Comparacion_Subzonas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,6 +640,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>empresas_2023</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>empresas_2024</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>empresas_2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>empresas_2026</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>crecimiento_empresas_%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_2023</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Deporte y recreación</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3" t="n">
+        <v>69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>198</v>
+      </c>
+      <c r="H3" t="n">
+        <v>203</v>
+      </c>
+      <c r="I3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>372</v>
+      </c>
+      <c r="C4" t="n">
+        <v>415</v>
+      </c>
+      <c r="D4" t="n">
+        <v>459</v>
+      </c>
+      <c r="E4" t="n">
+        <v>451</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8877</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9013</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1288,7 +1453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1550,132 +1715,6 @@
       </c>
       <c r="K6" t="n">
         <v>12.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>fuente</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>metodo_espacial</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Homicidios</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>sjoin within al polígono</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hurtos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>sjoin within al polígono</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Comparendos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sjoin within al polígono</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VIF</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sjoin within al polígono</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Siniestros</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sjoin within al polígono</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Desarrollo Económico</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sjoin within (Cámara geocodificada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Vivienda (SISBÉN)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sjoin + prorrateo por área (shapefile SISBÉN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Educación (Liceo Dptal)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sjoin de sedes al polígono (DANE 176001001745)</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -640,18 +640,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,37 +668,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>empresas_2024</t>
+          <t>empresas_2026</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>empresas_2025</t>
+          <t>crecimiento_empresas_%</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>empresas_2026</t>
+          <t>empleo_2023</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>crecimiento_empresas_%</t>
+          <t>empleo_2026</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>empleo_2023</t>
+          <t>ingresos_2023</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>empleo_2025</t>
+          <t>ingresos_2025</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>empleo_2026</t>
+          <t>ingresos_2026</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>crecimiento_ingresos_%</t>
         </is>
       </c>
     </row>
@@ -711,25 +717,28 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" t="n">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
-        <v>25</v>
-      </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>340691681</v>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>345691681</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>345691681</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -742,25 +751,28 @@
         <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>9.5</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="F3" t="n">
-        <v>9.5</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
-        <v>198</v>
+        <v>13464016318</v>
       </c>
       <c r="H3" t="n">
-        <v>203</v>
+        <v>13464016318</v>
       </c>
       <c r="I3" t="n">
-        <v>199</v>
+        <v>12693710318</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-5.7</v>
       </c>
     </row>
     <row r="4">
@@ -773,25 +785,28 @@
         <v>372</v>
       </c>
       <c r="C4" t="n">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="D4" t="n">
-        <v>459</v>
+        <v>21.2</v>
       </c>
       <c r="E4" t="n">
-        <v>451</v>
+        <v>8877</v>
       </c>
       <c r="F4" t="n">
-        <v>21.2</v>
+        <v>9002</v>
       </c>
       <c r="G4" t="n">
-        <v>8877</v>
+        <v>1651317119427</v>
       </c>
       <c r="H4" t="n">
-        <v>9013</v>
+        <v>2024384695875</v>
       </c>
       <c r="I4" t="n">
-        <v>9002</v>
+        <v>2024384695875</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -649,10 +649,8 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -688,22 +686,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ingresos_2023</t>
+          <t>empresas_con_ingreso</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ingresos_2025</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ingresos_2026</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>crecimiento_ingresos_%</t>
+          <t>ingresos_operacionales</t>
         </is>
       </c>
     </row>
@@ -729,17 +717,11 @@
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>340691681</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>345691681</v>
       </c>
-      <c r="I2" t="n">
-        <v>345691681</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -763,16 +745,10 @@
         <v>199</v>
       </c>
       <c r="G3" t="n">
-        <v>13464016318</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>13464016318</v>
-      </c>
-      <c r="I3" t="n">
         <v>12693710318</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-5.7</v>
       </c>
     </row>
     <row r="4">
@@ -797,16 +773,10 @@
         <v>9002</v>
       </c>
       <c r="G4" t="n">
-        <v>1651317119427</v>
+        <v>232</v>
       </c>
       <c r="H4" t="n">
         <v>2024384695875</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2024384695875</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
+++ b/outputs/itt_corredor_san_fernando/ITT_Corredor_San_Fernando_Consolidado.xlsx
@@ -640,17 +640,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,30 +671,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>empresas_2024</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>empresas_2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>empresas_2026</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>crecimiento_empresas_%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>empleo_2023</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_2024</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>empleo_2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>empleo_2026</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>crecimiento_empleo_%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>empresas_con_ingreso</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ingresos_operacionales</t>
         </is>
@@ -705,21 +735,36 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>25</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>18</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="M2" t="n">
         <v>345691681</v>
       </c>
     </row>
@@ -733,21 +778,36 @@
         <v>63</v>
       </c>
       <c r="C3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3" t="n">
         <v>69</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>9.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>198</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I3" t="n">
+        <v>203</v>
+      </c>
+      <c r="J3" t="n">
         <v>199</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
         <v>26</v>
       </c>
-      <c r="H3" t="n">
+      <c r="M3" t="n">
         <v>12693710318</v>
       </c>
     </row>
@@ -761,21 +821,36 @@
         <v>372</v>
       </c>
       <c r="C4" t="n">
+        <v>415</v>
+      </c>
+      <c r="D4" t="n">
+        <v>459</v>
+      </c>
+      <c r="E4" t="n">
         <v>451</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>21.2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>8877</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
+        <v>8959</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9013</v>
+      </c>
+      <c r="J4" t="n">
         <v>9002</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L4" t="n">
         <v>232</v>
       </c>
-      <c r="H4" t="n">
+      <c r="M4" t="n">
         <v>2024384695875</v>
       </c>
     </row>
